--- a/jpcore-r4/develop/ValueSet-jp-imagingstudy-endoscopy-bodysite-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-imagingstudy-endoscopy-bodysite-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
